--- a/XD_JIG/XD12/XD12_PWM_Rev_2/측정자료/XC24/xc24_osc_spread_250626.xlsx
+++ b/XD_JIG/XD12/XD12_PWM_Rev_2/측정자료/XC24/xc24_osc_spread_250626.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12_PWM_Rev_2\측정자료\XC24\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA33621C-FD2C-4884-B77E-A77CB5DD8A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFD94D2-559D-419E-8CDD-877DCF1718CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-255" windowWidth="29040" windowHeight="15720" xr2:uid="{607C7E93-A637-42E1-A86E-DBB62357E2BE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{607C7E93-A637-42E1-A86E-DBB62357E2BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
